--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:H46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B2" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-08</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B3" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
@@ -461,13 +461,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
@@ -481,13 +481,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
@@ -521,13 +521,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
@@ -581,13 +581,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
@@ -601,13 +601,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
@@ -621,13 +621,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
@@ -641,13 +641,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
@@ -701,13 +701,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -717,17 +717,23 @@
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -737,17 +743,23 @@
       </c>
       <c r="F17" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -757,17 +769,23 @@
       </c>
       <c r="F18" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -777,17 +795,23 @@
       </c>
       <c r="F19" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -797,17 +821,23 @@
       </c>
       <c r="F20" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -817,17 +847,23 @@
       </c>
       <c r="F21" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -837,17 +873,23 @@
       </c>
       <c r="F22" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -857,17 +899,23 @@
       </c>
       <c r="F23" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -877,17 +925,23 @@
       </c>
       <c r="F24" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -897,17 +951,23 @@
       </c>
       <c r="F25" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -917,17 +977,23 @@
       </c>
       <c r="F26" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -937,17 +1003,23 @@
       </c>
       <c r="F27" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -957,17 +1029,23 @@
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -977,17 +1055,23 @@
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -997,17 +1081,23 @@
       </c>
       <c r="F30" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1017,31 +1107,407 @@
       </c>
       <c r="F31" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2025  02:06 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
         <v>הרשם לחברות מלאה</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
         <v>https://rotter.name/nor/members-new.html</v>
       </c>
-      <c r="D32" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v>אלבומים חדשים</v>
+      <c r="D46" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:J59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,16 +421,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -441,16 +441,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B3" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -461,16 +461,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -481,16 +481,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B5" t="str">
         <v>2025  02:13-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -501,16 +501,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -521,16 +521,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -541,16 +541,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -561,16 +561,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -581,16 +581,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -601,16 +601,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -621,16 +621,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -641,16 +641,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -661,16 +661,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -681,13 +681,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
@@ -697,17 +697,23 @@
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -727,13 +733,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -753,13 +759,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -779,13 +785,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -805,13 +811,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -831,13 +837,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -857,13 +863,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -883,13 +889,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -909,13 +915,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -935,13 +941,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -961,13 +967,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -987,13 +993,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -1013,13 +1019,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -1039,13 +1045,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1060,18 +1066,24 @@
         <v/>
       </c>
       <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1086,18 +1098,24 @@
         <v/>
       </c>
       <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1112,18 +1130,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1138,18 +1162,24 @@
         <v/>
       </c>
       <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1164,18 +1194,24 @@
         <v/>
       </c>
       <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1190,18 +1226,24 @@
         <v/>
       </c>
       <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1216,18 +1258,24 @@
         <v/>
       </c>
       <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1242,18 +1290,24 @@
         <v/>
       </c>
       <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1268,18 +1322,24 @@
         <v/>
       </c>
       <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1294,18 +1354,24 @@
         <v/>
       </c>
       <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1320,18 +1386,24 @@
         <v/>
       </c>
       <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1346,18 +1418,24 @@
         <v/>
       </c>
       <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
@@ -1372,18 +1450,24 @@
         <v/>
       </c>
       <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1398,18 +1482,24 @@
         <v/>
       </c>
       <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1424,18 +1514,24 @@
         <v/>
       </c>
       <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1450,18 +1546,24 @@
         <v/>
       </c>
       <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1476,38 +1578,466 @@
         <v/>
       </c>
       <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>הרשם לחברות מלאה</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
-      </c>
-      <c r="C46" t="str">
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
         <v>https://rotter.name/nor/members-new.html</v>
       </c>
-      <c r="D46" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G46" t="str">
-        <v/>
-      </c>
-      <c r="H46" t="str">
+      <c r="D59" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J59"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:L72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,7 +421,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B2" t="str">
         <v>2026  11:38-01-09</v>
@@ -430,7 +430,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -441,7 +441,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B3" t="str">
         <v>2025  02:17-12-31</v>
@@ -450,7 +450,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -461,7 +461,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B4" t="str">
         <v>2025  02:16-12-31</v>
@@ -470,7 +470,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -481,7 +481,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B5" t="str">
         <v>2025  02:13-12-31</v>
@@ -490,7 +490,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -501,7 +501,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B6" t="str">
         <v>2025  02:12-12-31</v>
@@ -510,7 +510,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -521,7 +521,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B7" t="str">
         <v>2025  02:10-12-31</v>
@@ -530,7 +530,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -541,7 +541,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B8" t="str">
         <v>2025  02:09-12-31</v>
@@ -550,7 +550,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -561,7 +561,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B9" t="str">
         <v>2025  02:06-12-31</v>
@@ -570,7 +570,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -581,7 +581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B10" t="str">
         <v>2025  02:05-12-31</v>
@@ -590,7 +590,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -601,7 +601,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B11" t="str">
         <v>2025  02:03-12-31</v>
@@ -610,7 +610,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -621,7 +621,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B12" t="str">
         <v>2025  02:01-12-31</v>
@@ -630,7 +630,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -641,7 +641,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B13" t="str">
         <v>2025  01:57-12-31</v>
@@ -650,7 +650,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B14" t="str">
         <v>2025  01:55-12-31</v>
@@ -670,7 +670,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -681,16 +681,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -707,16 +707,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -733,16 +733,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -759,16 +759,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B18" t="str">
         <v>2025  02:13-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -785,16 +785,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -811,16 +811,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -837,16 +837,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -863,16 +863,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -889,16 +889,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -915,16 +915,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -941,16 +941,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -967,16 +967,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -993,16 +993,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1019,13 +1019,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -1040,18 +1040,24 @@
         <v/>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1077,13 +1083,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B30" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1109,13 +1115,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1141,13 +1147,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1173,13 +1179,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1205,13 +1211,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1237,13 +1243,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1269,13 +1275,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1301,13 +1307,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1333,13 +1339,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1365,13 +1371,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1397,13 +1403,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1429,13 +1435,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-08</v>
@@ -1461,13 +1467,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1488,18 +1494,24 @@
         <v/>
       </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1520,18 +1532,24 @@
         <v/>
       </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1552,18 +1570,24 @@
         <v/>
       </c>
       <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1584,18 +1608,24 @@
         <v/>
       </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1616,18 +1646,24 @@
         <v/>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1648,18 +1684,24 @@
         <v/>
       </c>
       <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1680,18 +1722,24 @@
         <v/>
       </c>
       <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1712,18 +1760,24 @@
         <v/>
       </c>
       <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -1744,18 +1798,24 @@
         <v/>
       </c>
       <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -1776,18 +1836,24 @@
         <v/>
       </c>
       <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -1808,18 +1874,24 @@
         <v/>
       </c>
       <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -1840,18 +1912,24 @@
         <v/>
       </c>
       <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -1872,18 +1950,24 @@
         <v/>
       </c>
       <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -1904,18 +1988,24 @@
         <v/>
       </c>
       <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -1936,18 +2026,24 @@
         <v/>
       </c>
       <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -1968,18 +2064,24 @@
         <v/>
       </c>
       <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2000,44 +2102,550 @@
         <v/>
       </c>
       <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
         <v>הרשם לחברות מלאה</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
-      </c>
-      <c r="C59" t="str">
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
         <v>https://rotter.name/nor/members-new.html</v>
       </c>
-      <c r="D59" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="J59" t="str">
+      <c r="D72" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L72"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:N86"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,16 +421,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C2" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -441,16 +441,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -461,16 +461,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -481,16 +481,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -501,16 +501,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -521,16 +521,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -541,16 +541,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -561,16 +561,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -581,16 +581,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -601,16 +601,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -621,16 +621,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -641,16 +641,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -661,16 +661,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -681,42 +681,36 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B15" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -733,16 +727,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -759,16 +753,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -785,16 +779,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -811,16 +805,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -837,16 +831,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -863,16 +857,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -889,16 +883,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -915,16 +909,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -941,16 +935,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -967,16 +961,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -993,16 +987,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1019,16 +1013,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1040,27 +1034,21 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1083,16 +1071,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1115,16 +1103,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1147,16 +1135,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1179,16 +1167,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1211,16 +1199,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1243,16 +1231,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1275,16 +1263,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1307,16 +1295,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1339,16 +1327,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1371,16 +1359,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1403,16 +1391,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1435,16 +1423,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1467,13 +1455,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-08</v>
@@ -1505,13 +1493,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B43" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1543,13 +1531,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B44" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1581,13 +1569,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1619,13 +1607,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1657,13 +1645,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1695,13 +1683,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1733,13 +1721,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1771,13 +1759,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -1809,13 +1797,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -1847,13 +1835,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -1885,13 +1873,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -1923,13 +1911,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -1961,13 +1949,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -1999,13 +1987,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2032,18 +2020,24 @@
         <v/>
       </c>
       <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2070,18 +2064,24 @@
         <v/>
       </c>
       <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2108,18 +2108,24 @@
         <v/>
       </c>
       <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2146,18 +2152,24 @@
         <v/>
       </c>
       <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2184,18 +2196,24 @@
         <v/>
       </c>
       <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B61" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
@@ -2222,18 +2240,24 @@
         <v/>
       </c>
       <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
@@ -2260,18 +2284,24 @@
         <v/>
       </c>
       <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
@@ -2298,18 +2328,24 @@
         <v/>
       </c>
       <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
@@ -2336,18 +2372,24 @@
         <v/>
       </c>
       <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
@@ -2374,18 +2416,24 @@
         <v/>
       </c>
       <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
@@ -2412,18 +2460,24 @@
         <v/>
       </c>
       <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
@@ -2450,18 +2504,24 @@
         <v/>
       </c>
       <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
@@ -2488,18 +2548,24 @@
         <v/>
       </c>
       <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
@@ -2526,18 +2592,24 @@
         <v/>
       </c>
       <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
@@ -2564,18 +2636,24 @@
         <v/>
       </c>
       <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -2602,50 +2680,678 @@
         <v/>
       </c>
       <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2025  02:06 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C82" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C83" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C84" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C85" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
         <v>הרשם לחברות מלאה</v>
       </c>
-      <c r="B72" t="str">
-        <v/>
-      </c>
-      <c r="C72" t="str">
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
         <v>https://rotter.name/nor/members-new.html</v>
       </c>
-      <c r="D72" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E72" t="str">
-        <v/>
-      </c>
-      <c r="F72" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G72" t="str">
-        <v/>
-      </c>
-      <c r="H72" t="str">
-        <v/>
-      </c>
-      <c r="I72" t="str">
-        <v/>
-      </c>
-      <c r="J72" t="str">
-        <v/>
-      </c>
-      <c r="K72" t="str">
-        <v/>
-      </c>
-      <c r="L72" t="str">
+      <c r="D86" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N86"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:P87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-15</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B3" t="str">
         <v>2026  08:40-01-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-15</v>
@@ -458,16 +458,22 @@
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-15</v>
@@ -478,16 +484,22 @@
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-15</v>
@@ -498,16 +510,22 @@
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-15</v>
@@ -518,16 +536,22 @@
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-15</v>
@@ -538,16 +562,22 @@
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-15</v>
@@ -558,16 +588,22 @@
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
@@ -578,16 +614,22 @@
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
@@ -598,16 +640,22 @@
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
@@ -618,16 +666,22 @@
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
@@ -638,16 +692,22 @@
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
@@ -658,16 +718,22 @@
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
@@ -678,16 +744,22 @@
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יוני רועה - מפוזרים</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
@@ -698,19 +770,25 @@
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B16" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -727,13 +805,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B17" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-10</v>
@@ -750,16 +828,22 @@
       <c r="H17" t="str">
         <v/>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-10</v>
@@ -776,16 +860,22 @@
       <c r="H18" t="str">
         <v/>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-10</v>
@@ -802,16 +892,22 @@
       <c r="H19" t="str">
         <v/>
       </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-10</v>
@@ -828,16 +924,22 @@
       <c r="H20" t="str">
         <v/>
       </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-10</v>
@@ -854,16 +956,22 @@
       <c r="H21" t="str">
         <v/>
       </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-10</v>
@@ -880,16 +988,22 @@
       <c r="H22" t="str">
         <v/>
       </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-10</v>
@@ -906,16 +1020,22 @@
       <c r="H23" t="str">
         <v/>
       </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-10</v>
@@ -932,16 +1052,22 @@
       <c r="H24" t="str">
         <v/>
       </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-10</v>
@@ -958,16 +1084,22 @@
       <c r="H25" t="str">
         <v/>
       </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-10</v>
@@ -984,16 +1116,22 @@
       <c r="H26" t="str">
         <v/>
       </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-10</v>
@@ -1010,16 +1148,22 @@
       <c r="H27" t="str">
         <v/>
       </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-10</v>
@@ -1036,19 +1180,25 @@
       <c r="H28" t="str">
         <v/>
       </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B29" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1071,13 +1221,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-09</v>
@@ -1100,16 +1250,22 @@
       <c r="J30" t="str">
         <v/>
       </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-09</v>
@@ -1132,16 +1288,22 @@
       <c r="J31" t="str">
         <v/>
       </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-09</v>
@@ -1164,16 +1326,22 @@
       <c r="J32" t="str">
         <v/>
       </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-09</v>
@@ -1196,16 +1364,22 @@
       <c r="J33" t="str">
         <v/>
       </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-09</v>
@@ -1228,16 +1402,22 @@
       <c r="J34" t="str">
         <v/>
       </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-09</v>
@@ -1260,16 +1440,22 @@
       <c r="J35" t="str">
         <v/>
       </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-09</v>
@@ -1292,16 +1478,22 @@
       <c r="J36" t="str">
         <v/>
       </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-09</v>
@@ -1324,16 +1516,22 @@
       <c r="J37" t="str">
         <v/>
       </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-09</v>
@@ -1356,16 +1554,22 @@
       <c r="J38" t="str">
         <v/>
       </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-09</v>
@@ -1388,16 +1592,22 @@
       <c r="J39" t="str">
         <v/>
       </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-09</v>
@@ -1420,16 +1630,22 @@
       <c r="J40" t="str">
         <v/>
       </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-09</v>
@@ -1452,19 +1668,25 @@
       <c r="J41" t="str">
         <v/>
       </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1493,13 +1715,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-08</v>
@@ -1526,18 +1748,24 @@
         <v/>
       </c>
       <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-08</v>
@@ -1564,18 +1792,24 @@
         <v/>
       </c>
       <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-08</v>
@@ -1602,18 +1836,24 @@
         <v/>
       </c>
       <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-08</v>
@@ -1640,18 +1880,24 @@
         <v/>
       </c>
       <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-08</v>
@@ -1678,18 +1924,24 @@
         <v/>
       </c>
       <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1716,18 +1968,24 @@
         <v/>
       </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1754,18 +2012,24 @@
         <v/>
       </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -1792,18 +2056,24 @@
         <v/>
       </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -1830,18 +2100,24 @@
         <v/>
       </c>
       <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -1868,18 +2144,24 @@
         <v/>
       </c>
       <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -1906,18 +2188,24 @@
         <v/>
       </c>
       <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -1944,18 +2232,24 @@
         <v/>
       </c>
       <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -1982,18 +2276,24 @@
         <v/>
       </c>
       <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2031,13 +2331,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B57" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2070,18 +2370,24 @@
         <v/>
       </c>
       <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B58" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2114,18 +2420,24 @@
         <v/>
       </c>
       <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2158,18 +2470,24 @@
         <v/>
       </c>
       <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2202,18 +2520,24 @@
         <v/>
       </c>
       <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B61" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
@@ -2246,18 +2570,24 @@
         <v/>
       </c>
       <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B62" t="str">
         <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
@@ -2290,18 +2620,24 @@
         <v/>
       </c>
       <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
@@ -2334,18 +2670,24 @@
         <v/>
       </c>
       <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
@@ -2378,18 +2720,24 @@
         <v/>
       </c>
       <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B65" t="str">
         <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
@@ -2422,18 +2770,24 @@
         <v/>
       </c>
       <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
@@ -2466,18 +2820,24 @@
         <v/>
       </c>
       <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
@@ -2510,18 +2870,24 @@
         <v/>
       </c>
       <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
@@ -2554,18 +2920,24 @@
         <v/>
       </c>
       <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
@@ -2598,18 +2970,24 @@
         <v/>
       </c>
       <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B70" t="str">
         <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
@@ -2642,18 +3020,24 @@
         <v/>
       </c>
       <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -2686,18 +3070,24 @@
         <v/>
       </c>
       <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B72" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
@@ -2730,18 +3120,24 @@
         <v/>
       </c>
       <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B73" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
@@ -2774,18 +3170,24 @@
         <v/>
       </c>
       <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
       </c>
       <c r="B74" t="str">
         <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
@@ -2818,18 +3220,24 @@
         <v/>
       </c>
       <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
       </c>
       <c r="B75" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:05 מאת DiSHi-12-31</v>
       </c>
       <c r="C75" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
@@ -2862,18 +3270,24 @@
         <v/>
       </c>
       <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
       </c>
       <c r="B76" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:04 מאת DiSHi-12-31</v>
       </c>
       <c r="C76" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
@@ -2906,18 +3320,24 @@
         <v/>
       </c>
       <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
       </c>
       <c r="B77" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:03 מאת DiSHi-12-31</v>
       </c>
       <c r="C77" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
@@ -2950,18 +3370,24 @@
         <v/>
       </c>
       <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:02 מאת DiSHi-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
@@ -2994,18 +3420,24 @@
         <v/>
       </c>
       <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:01 מאת DiSHi-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
@@ -3038,18 +3470,24 @@
         <v/>
       </c>
       <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:00 מאת DiSHi-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
@@ -3082,18 +3520,24 @@
         <v/>
       </c>
       <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  01:57 מאת DiSHi-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
@@ -3126,18 +3570,24 @@
         <v/>
       </c>
       <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  01:56 מאת DiSHi-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
@@ -3170,18 +3620,24 @@
         <v/>
       </c>
       <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  01:55 מאת DiSHi-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
@@ -3214,18 +3670,24 @@
         <v/>
       </c>
       <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  01:54 מאת DiSHi-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
@@ -3258,18 +3720,24 @@
         <v/>
       </c>
       <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
       </c>
       <c r="B85" t="str">
         <v>2025  01:53 מאת DiSHi-12-31</v>
       </c>
       <c r="C85" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
@@ -3302,56 +3770,118 @@
         <v/>
       </c>
       <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C86" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>הרשם לחברות מלאה</v>
       </c>
-      <c r="B86" t="str">
-        <v/>
-      </c>
-      <c r="C86" t="str">
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
         <v>https://rotter.name/nor/members-new.html</v>
       </c>
-      <c r="D86" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E86" t="str">
-        <v/>
-      </c>
-      <c r="F86" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G86" t="str">
-        <v/>
-      </c>
-      <c r="H86" t="str">
-        <v/>
-      </c>
-      <c r="I86" t="str">
-        <v/>
-      </c>
-      <c r="J86" t="str">
-        <v/>
-      </c>
-      <c r="K86" t="str">
-        <v/>
-      </c>
-      <c r="L86" t="str">
-        <v/>
-      </c>
-      <c r="M86" t="str">
-        <v/>
-      </c>
-      <c r="N86" t="str">
+      <c r="D87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:T101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,7 +416,22 @@
         <v>תיאור</v>
       </c>
       <c r="F1" t="str">
+        <v>משך</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ערוץ</v>
+      </c>
+      <c r="H1" t="str">
         <v>תגית</v>
+      </c>
+      <c r="I1" t="str">
+        <v>קישור אמן</v>
+      </c>
+      <c r="J1" t="str">
+        <v>קישור אלבום</v>
+      </c>
+      <c r="K1" t="str">
+        <v>שיר - אמן</v>
       </c>
     </row>
     <row r="2">
@@ -436,18 +451,33 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026  08:40-01-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-15</v>
@@ -456,24 +486,33 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-15</v>
@@ -482,24 +521,33 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>אייל גולן - בית מפואר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-15</v>
@@ -508,24 +556,33 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-15</v>
@@ -534,24 +591,33 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>שיר לוי - ילד מוזר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-15</v>
@@ -560,24 +626,33 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>פיטר רוט - 50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-15</v>
@@ -586,24 +661,33 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
@@ -612,24 +696,33 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
@@ -638,24 +731,33 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
@@ -664,24 +766,33 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
@@ -690,24 +801,33 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
@@ -716,24 +836,33 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
@@ -742,24 +871,33 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
@@ -768,24 +906,33 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>יוני רועה - מפוזרים</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>יוני רועה - מפוזרים</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-15</v>
@@ -802,19 +949,25 @@
       <c r="H16" t="str">
         <v/>
       </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B17" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C17" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -832,21 +985,27 @@
         <v/>
       </c>
       <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -864,21 +1023,27 @@
         <v/>
       </c>
       <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -896,21 +1061,27 @@
         <v/>
       </c>
       <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -928,21 +1099,27 @@
         <v/>
       </c>
       <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -960,21 +1137,27 @@
         <v/>
       </c>
       <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -992,21 +1175,27 @@
         <v/>
       </c>
       <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1024,21 +1213,27 @@
         <v/>
       </c>
       <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1056,21 +1251,27 @@
         <v/>
       </c>
       <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1088,21 +1289,27 @@
         <v/>
       </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1120,21 +1327,27 @@
         <v/>
       </c>
       <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1152,21 +1365,27 @@
         <v/>
       </c>
       <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1184,21 +1403,27 @@
         <v/>
       </c>
       <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1216,21 +1441,27 @@
         <v/>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B30" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1259,16 +1490,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B31" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C31" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1292,21 +1523,27 @@
         <v/>
       </c>
       <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1330,21 +1567,27 @@
         <v/>
       </c>
       <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1368,21 +1611,27 @@
         <v/>
       </c>
       <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1406,21 +1655,27 @@
         <v/>
       </c>
       <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1444,21 +1699,27 @@
         <v/>
       </c>
       <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1482,21 +1743,27 @@
         <v/>
       </c>
       <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1520,21 +1787,27 @@
         <v/>
       </c>
       <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1558,21 +1831,27 @@
         <v/>
       </c>
       <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1596,21 +1875,27 @@
         <v/>
       </c>
       <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1634,21 +1919,27 @@
         <v/>
       </c>
       <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1672,21 +1963,27 @@
         <v/>
       </c>
       <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1710,21 +2007,27 @@
         <v/>
       </c>
       <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1759,16 +2062,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1798,21 +2101,27 @@
         <v/>
       </c>
       <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1842,21 +2151,27 @@
         <v/>
       </c>
       <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1886,21 +2201,27 @@
         <v/>
       </c>
       <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1930,21 +2251,27 @@
         <v/>
       </c>
       <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1974,21 +2301,27 @@
         <v/>
       </c>
       <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2018,21 +2351,27 @@
         <v/>
       </c>
       <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2062,21 +2401,27 @@
         <v/>
       </c>
       <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2106,21 +2451,27 @@
         <v/>
       </c>
       <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2150,21 +2501,27 @@
         <v/>
       </c>
       <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2194,21 +2551,27 @@
         <v/>
       </c>
       <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2238,21 +2601,27 @@
         <v/>
       </c>
       <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2282,21 +2651,27 @@
         <v/>
       </c>
       <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2326,18 +2701,24 @@
         <v/>
       </c>
       <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-08</v>
@@ -2378,16 +2759,22 @@
       <c r="P57" t="str">
         <v/>
       </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B58" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-08</v>
@@ -2428,16 +2815,22 @@
       <c r="P58" t="str">
         <v/>
       </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B59" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-08</v>
@@ -2478,16 +2871,22 @@
       <c r="P59" t="str">
         <v/>
       </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-08</v>
@@ -2528,16 +2927,22 @@
       <c r="P60" t="str">
         <v/>
       </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B61" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-08</v>
@@ -2578,16 +2983,22 @@
       <c r="P61" t="str">
         <v/>
       </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-08</v>
@@ -2628,16 +3039,22 @@
       <c r="P62" t="str">
         <v/>
       </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-08</v>
@@ -2678,16 +3095,22 @@
       <c r="P63" t="str">
         <v/>
       </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-08</v>
@@ -2728,16 +3151,22 @@
       <c r="P64" t="str">
         <v/>
       </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-08</v>
@@ -2778,16 +3207,22 @@
       <c r="P65" t="str">
         <v/>
       </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-08</v>
@@ -2828,16 +3263,22 @@
       <c r="P66" t="str">
         <v/>
       </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-08</v>
@@ -2878,16 +3319,22 @@
       <c r="P67" t="str">
         <v/>
       </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-08</v>
@@ -2928,16 +3375,22 @@
       <c r="P68" t="str">
         <v/>
       </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-08</v>
@@ -2978,16 +3431,22 @@
       <c r="P69" t="str">
         <v/>
       </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-08</v>
@@ -3028,16 +3487,22 @@
       <c r="P70" t="str">
         <v/>
       </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -3078,16 +3543,28 @@
       <c r="P71" t="str">
         <v/>
       </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B72" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
@@ -3128,16 +3605,28 @@
       <c r="P72" t="str">
         <v/>
       </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B73" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
@@ -3178,16 +3667,28 @@
       <c r="P73" t="str">
         <v/>
       </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B74" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
@@ -3228,16 +3729,28 @@
       <c r="P74" t="str">
         <v/>
       </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B75" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C75" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
@@ -3278,16 +3791,28 @@
       <c r="P75" t="str">
         <v/>
       </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B76" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C76" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
@@ -3328,16 +3853,28 @@
       <c r="P76" t="str">
         <v/>
       </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B77" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C77" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
@@ -3378,16 +3915,28 @@
       <c r="P77" t="str">
         <v/>
       </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
@@ -3428,16 +3977,28 @@
       <c r="P78" t="str">
         <v/>
       </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
@@ -3478,16 +4039,28 @@
       <c r="P79" t="str">
         <v/>
       </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
@@ -3528,16 +4101,28 @@
       <c r="P80" t="str">
         <v/>
       </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
@@ -3578,16 +4163,28 @@
       <c r="P81" t="str">
         <v/>
       </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+      <c r="T81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
@@ -3628,16 +4225,28 @@
       <c r="P82" t="str">
         <v/>
       </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+      <c r="T82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
@@ -3678,16 +4287,28 @@
       <c r="P83" t="str">
         <v/>
       </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+      <c r="T83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
@@ -3728,16 +4349,28 @@
       <c r="P84" t="str">
         <v/>
       </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B85" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C85" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
@@ -3778,16 +4411,28 @@
       <c r="P85" t="str">
         <v/>
       </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+      <c r="T85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B86" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C86" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
@@ -3828,16 +4473,28 @@
       <c r="P86" t="str">
         <v/>
       </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+      <c r="T86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B87" t="str">
-        <v/>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C87" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
@@ -3878,10 +4535,890 @@
       <c r="P87" t="str">
         <v/>
       </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+      <c r="T87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C88" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+      <c r="T88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C89" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+      <c r="T89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C90" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C91" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+      <c r="T91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C92" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C93" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C94" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C95" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C96" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C97" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C98" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C99" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C100" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>הרשם לחברות מלאה</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://rotter.name/nor/members-new.html</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:X115"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -941,30 +941,45 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B17" t="str">
         <v>2026  08:40-01-14</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-15</v>
@@ -973,13 +988,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -988,21 +1003,30 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B18" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-15</v>
@@ -1011,13 +1035,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1026,21 +1050,30 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-15</v>
@@ -1049,13 +1082,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1064,21 +1097,30 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-15</v>
@@ -1087,13 +1129,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1102,21 +1144,30 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-15</v>
@@ -1125,13 +1176,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1140,21 +1191,30 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-15</v>
@@ -1163,13 +1223,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1178,21 +1238,30 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-15</v>
@@ -1201,13 +1270,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1216,21 +1285,30 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-15</v>
@@ -1239,13 +1317,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1254,21 +1332,30 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-15</v>
@@ -1277,13 +1364,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1292,21 +1379,30 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-15</v>
@@ -1315,13 +1411,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1330,21 +1426,30 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-15</v>
@@ -1353,13 +1458,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1368,21 +1473,30 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-15</v>
@@ -1391,13 +1505,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1406,21 +1520,30 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-15</v>
@@ -1429,13 +1552,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1444,21 +1567,30 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>יוני רועה - מפוזרים</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B30" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C30" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-15</v>
@@ -1487,19 +1619,25 @@
       <c r="L30" t="str">
         <v/>
       </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B31" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C31" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1529,21 +1667,27 @@
         <v/>
       </c>
       <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B32" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C32" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1573,21 +1717,27 @@
         <v/>
       </c>
       <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>|אלבום חדש| אברהם טל - חי ()</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B33" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C33" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1617,21 +1767,27 @@
         <v/>
       </c>
       <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B34" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C34" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1661,21 +1817,27 @@
         <v/>
       </c>
       <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B35" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C35" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1705,21 +1867,27 @@
         <v/>
       </c>
       <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B36" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1749,21 +1917,27 @@
         <v/>
       </c>
       <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B37" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C37" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1793,21 +1967,27 @@
         <v/>
       </c>
       <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B38" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C38" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1837,21 +2017,27 @@
         <v/>
       </c>
       <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B39" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C39" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1881,21 +2067,27 @@
         <v/>
       </c>
       <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B40" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C40" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1925,21 +2117,27 @@
         <v/>
       </c>
       <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B41" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C41" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1969,21 +2167,27 @@
         <v/>
       </c>
       <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B42" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C42" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2013,21 +2217,27 @@
         <v/>
       </c>
       <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה ()</v>
+        <v>שלמה גרוניך - כמו כוכבים</v>
       </c>
       <c r="B43" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C43" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-10</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2057,21 +2267,27 @@
         <v/>
       </c>
       <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>|| תומר יוסף - 360 (2026)</v>
+        <v>יוני רועה - מפוזרים</v>
       </c>
       <c r="B44" t="str">
-        <v>2026  11:38-01-09</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C44" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2112,16 +2328,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
+        <v>|אלבום חדש| תומר יוסף - 360 ()</v>
       </c>
       <c r="B45" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C45" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2157,21 +2373,27 @@
         <v/>
       </c>
       <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>|| אברהם טל - חי ()</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B46" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C46" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2207,21 +2429,27 @@
         <v/>
       </c>
       <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>|| מיקי גבריאלוב - שלום ()</v>
+        <v>|אלבום חדש| אברהם טל - חי ()</v>
       </c>
       <c r="B47" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C47" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2257,21 +2485,27 @@
         <v/>
       </c>
       <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B48" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C48" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2307,21 +2541,27 @@
         <v/>
       </c>
       <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B49" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C49" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2357,21 +2597,27 @@
         <v/>
       </c>
       <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>|| שלמה גרוניך - תודה אהבה ()</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B50" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C50" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2407,21 +2653,27 @@
         <v/>
       </c>
       <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B51" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2457,21 +2709,27 @@
         <v/>
       </c>
       <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B52" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C52" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2507,21 +2765,27 @@
         <v/>
       </c>
       <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>|| סטטיק - קעקועים ()</v>
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B53" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C53" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2557,21 +2821,27 @@
         <v/>
       </c>
       <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>|| ליאור נרקיס - דיסוננס ()</v>
+        <v>|אלבום חדש| סטטיק - קעקועים ()</v>
       </c>
       <c r="B54" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C54" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2607,21 +2877,27 @@
         <v/>
       </c>
       <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B55" t="str">
-        <v>2025  01:57-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C55" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2657,21 +2933,27 @@
         <v/>
       </c>
       <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>|| אתניקס - איטליה ()</v>
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B56" t="str">
-        <v>2025  01:55-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C56" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2707,21 +2989,27 @@
         <v/>
       </c>
       <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>|| אייל גולן - בית מפואר ()</v>
+        <v>|אלבום חדש| אתניקס - איטליה ()</v>
       </c>
       <c r="B57" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C57" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2768,16 +3056,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
+        <v>|| תומר יוסף - 360 (2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2026  11:38-01-09</v>
       </c>
       <c r="C58" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2819,21 +3107,27 @@
         <v/>
       </c>
       <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v/>
+      </c>
+      <c r="T58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>|| שיר לוי - ילד מוזר ()</v>
+        <v>|| עמיר בניון - לא נוגע בקרקע ()</v>
       </c>
       <c r="B59" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2025  02:17-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2875,21 +3169,27 @@
         <v/>
       </c>
       <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
+      <c r="T59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>|| פיטר רוט - 50 ()</v>
+        <v>|| אברהם טל - חי ()</v>
       </c>
       <c r="B60" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C60" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2931,21 +3231,27 @@
         <v/>
       </c>
       <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
+        <v>|| מיקי גבריאלוב - שלום ()</v>
       </c>
       <c r="B61" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C61" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2987,21 +3293,27 @@
         <v/>
       </c>
       <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+      <c r="T61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>|| רבקה זוהר - רסיסים של אור ()</v>
+        <v>|| בזכרי ימים ימימה - מחווה לצלילי הכרם ()</v>
       </c>
       <c r="B62" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>2025  02:12-12-31</v>
       </c>
       <c r="C62" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -3043,21 +3355,27 @@
         <v/>
       </c>
       <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+      <c r="T62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
+        <v>|| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון ()</v>
       </c>
       <c r="B63" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>2025  02:10-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -3099,21 +3417,27 @@
         <v/>
       </c>
       <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+      <c r="T63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
+        <v>|| שלמה גרוניך - תודה אהבה ()</v>
       </c>
       <c r="B64" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C64" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -3155,21 +3479,27 @@
         <v/>
       </c>
       <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+      <c r="T64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
+        <v>|| חוה אלברשטיין - חמישה שירים ()</v>
       </c>
       <c r="B65" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>2025  02:06-12-31</v>
       </c>
       <c r="C65" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -3211,21 +3541,27 @@
         <v/>
       </c>
       <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>|| השמחות - חובות אבודים ()</v>
+        <v>|| הפרויקט של עידן רייכל - עד סוף העולם ()</v>
       </c>
       <c r="B66" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C66" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -3267,21 +3603,27 @@
         <v/>
       </c>
       <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+      <c r="T66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
+        <v>|| סטטיק - קעקועים ()</v>
       </c>
       <c r="B67" t="str">
-        <v>2025  02:00-12-31</v>
+        <v>2025  02:03-12-31</v>
       </c>
       <c r="C67" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -3323,21 +3665,27 @@
         <v/>
       </c>
       <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+      <c r="T67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>|| יוני רועה - מפוזרים ()</v>
+        <v>|| ליאור נרקיס - דיסוננס ()</v>
       </c>
       <c r="B68" t="str">
-        <v>2025  01:56-12-31</v>
+        <v>2025  02:01-12-31</v>
       </c>
       <c r="C68" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -3379,21 +3727,27 @@
         <v/>
       </c>
       <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+      <c r="T68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>|| התקווה 6 - ויהי אור ()</v>
+        <v>|| דיוויד ברוזה - BrozaJazz (Paris Alhambra) ()</v>
       </c>
       <c r="B69" t="str">
-        <v>2025  01:54-12-31</v>
+        <v>2025  01:57-12-31</v>
       </c>
       <c r="C69" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3435,21 +3789,27 @@
         <v/>
       </c>
       <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
+        <v>|| אתניקס - איטליה ()</v>
       </c>
       <c r="B70" t="str">
-        <v>2025  01:53-12-31</v>
+        <v>2025  01:55-12-31</v>
       </c>
       <c r="C70" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3491,18 +3851,24 @@
         <v/>
       </c>
       <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+      <c r="T70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>אשכול נוכחות למשתמשים פעילים</v>
+        <v>|| אייל גולן - בית מפואר ()</v>
       </c>
       <c r="B71" t="str">
-        <v>2025  16:32 מאת freund-10-16</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C71" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-08</v>
@@ -3555,16 +3921,22 @@
       <c r="T71" t="str">
         <v/>
       </c>
+      <c r="U71" t="str">
+        <v/>
+      </c>
+      <c r="V71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>כיצד להוריד מהאתרים המפורסמים</v>
+        <v>|| הפרויקט של דודי לוי ואבטיפוס - הפטריקים ()</v>
       </c>
       <c r="B72" t="str">
-        <v>2023  16:23 מאת petel1-08-08</v>
+        <v>2025  02:16-12-31</v>
       </c>
       <c r="C72" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-08</v>
@@ -3617,16 +3989,22 @@
       <c r="T72" t="str">
         <v/>
       </c>
+      <c r="U72" t="str">
+        <v/>
+      </c>
+      <c r="V72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>|| שיר לוי - ילד מוזר ()</v>
       </c>
       <c r="B73" t="str">
-        <v>2026  22:40 מאת מוטי_ד-01-01</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C73" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-08</v>
@@ -3679,16 +4057,22 @@
       <c r="T73" t="str">
         <v/>
       </c>
+      <c r="U73" t="str">
+        <v/>
+      </c>
+      <c r="V73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
+        <v>|| פיטר רוט - 50 ()</v>
       </c>
       <c r="B74" t="str">
-        <v>2025  02:18 מאת DiSHi-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C74" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-08</v>
@@ -3741,16 +4125,22 @@
       <c r="T74" t="str">
         <v/>
       </c>
+      <c r="U74" t="str">
+        <v/>
+      </c>
+      <c r="V74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>|| אגם בוחבוט - עשרים ואחת ()</v>
       </c>
       <c r="B75" t="str">
-        <v>2025  02:17 מאת DiSHi-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C75" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-08</v>
@@ -3803,16 +4193,22 @@
       <c r="T75" t="str">
         <v/>
       </c>
+      <c r="U75" t="str">
+        <v/>
+      </c>
+      <c r="V75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
+        <v>|| רבקה זוהר - רסיסים של אור ()</v>
       </c>
       <c r="B76" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:09-12-31</v>
       </c>
       <c r="C76" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-08</v>
@@ -3865,16 +4261,22 @@
       <c r="T76" t="str">
         <v/>
       </c>
+      <c r="U76" t="str">
+        <v/>
+      </c>
+      <c r="V76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>|| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות ()</v>
       </c>
       <c r="B77" t="str">
-        <v>2025  02:16 מאת DiSHi-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C77" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-08</v>
@@ -3927,16 +4329,22 @@
       <c r="T77" t="str">
         <v/>
       </c>
+      <c r="U77" t="str">
+        <v/>
+      </c>
+      <c r="V77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
+        <v>|| אהוד בנאי ובנו הנדלר - פליטי הדאב ()</v>
       </c>
       <c r="B78" t="str">
-        <v>2025  02:14 מאת DiSHi-12-31</v>
+        <v>2025  02:05-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
@@ -3989,16 +4397,22 @@
       <c r="T78" t="str">
         <v/>
       </c>
+      <c r="U78" t="str">
+        <v/>
+      </c>
+      <c r="V78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>|| Imagine פסטיגל - שירי התחרות ()</v>
       </c>
       <c r="B79" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C79" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
@@ -4051,16 +4465,22 @@
       <c r="T79" t="str">
         <v/>
       </c>
+      <c r="U79" t="str">
+        <v/>
+      </c>
+      <c r="V79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
+        <v>|| השמחות - חובות אבודים ()</v>
       </c>
       <c r="B80" t="str">
-        <v>2025  02:13 מאת DiSHi-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C80" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
@@ -4113,16 +4533,22 @@
       <c r="T80" t="str">
         <v/>
       </c>
+      <c r="U80" t="str">
+        <v/>
+      </c>
+      <c r="V80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>|| שלמה גרוניך - כמו כוכבים ()</v>
       </c>
       <c r="B81" t="str">
-        <v>2025  02:12 מאת DiSHi-12-31</v>
+        <v>2025  02:00-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
@@ -4175,16 +4601,22 @@
       <c r="T81" t="str">
         <v/>
       </c>
+      <c r="U81" t="str">
+        <v/>
+      </c>
+      <c r="V81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
+        <v>|| יוני רועה - מפוזרים ()</v>
       </c>
       <c r="B82" t="str">
-        <v>2025  02:11 מאת DiSHi-12-31</v>
+        <v>2025  01:56-12-31</v>
       </c>
       <c r="C82" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
@@ -4237,16 +4669,22 @@
       <c r="T82" t="str">
         <v/>
       </c>
+      <c r="U82" t="str">
+        <v/>
+      </c>
+      <c r="V82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>|| התקווה 6 - ויהי אור ()</v>
       </c>
       <c r="B83" t="str">
-        <v>2025  02:10 מאת DiSHi-12-31</v>
+        <v>2025  01:54-12-31</v>
       </c>
       <c r="C83" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
@@ -4299,16 +4737,22 @@
       <c r="T83" t="str">
         <v/>
       </c>
+      <c r="U83" t="str">
+        <v/>
+      </c>
+      <c r="V83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
+        <v>|| שאנן סטריט ודי ג׳יי מש - באתי לבדר ()</v>
       </c>
       <c r="B84" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  01:53-12-31</v>
       </c>
       <c r="C84" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
@@ -4361,16 +4805,22 @@
       <c r="T84" t="str">
         <v/>
       </c>
+      <c r="U84" t="str">
+        <v/>
+      </c>
+      <c r="V84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>אשכול נוכחות למשתמשים פעילים</v>
       </c>
       <c r="B85" t="str">
-        <v>2025  02:09 מאת DiSHi-12-31</v>
+        <v>2025  16:32 מאת freund-10-16</v>
       </c>
       <c r="C85" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
@@ -4423,16 +4873,28 @@
       <c r="T85" t="str">
         <v/>
       </c>
+      <c r="U85" t="str">
+        <v/>
+      </c>
+      <c r="V85" t="str">
+        <v/>
+      </c>
+      <c r="W85" t="str">
+        <v/>
+      </c>
+      <c r="X85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
+        <v>כיצד להוריד מהאתרים המפורסמים</v>
       </c>
       <c r="B86" t="str">
-        <v>2025  02:08 מאת DiSHi-12-31</v>
+        <v>2023  16:23 מאת petel1-08-08</v>
       </c>
       <c r="C86" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=22411&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
@@ -4485,16 +4947,28 @@
       <c r="T86" t="str">
         <v/>
       </c>
+      <c r="U86" t="str">
+        <v/>
+      </c>
+      <c r="V86" t="str">
+        <v/>
+      </c>
+      <c r="W86" t="str">
+        <v/>
+      </c>
+      <c r="X86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B87" t="str">
-        <v>2025  02:06 מאת DiSHi-12-31</v>
+        <v>2026  22:40 מאת מוטי_ד-01-01</v>
       </c>
       <c r="C87" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
@@ -4547,16 +5021,28 @@
       <c r="T87" t="str">
         <v/>
       </c>
+      <c r="U87" t="str">
+        <v/>
+      </c>
+      <c r="V87" t="str">
+        <v/>
+      </c>
+      <c r="W87" t="str">
+        <v/>
+      </c>
+      <c r="X87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+        <v>|אלבום חדש| אייל גולן - בית מפואר (2025)</v>
       </c>
       <c r="B88" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:18 מאת DiSHi-12-31</v>
       </c>
       <c r="C88" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-08</v>
@@ -4609,16 +5095,28 @@
       <c r="T88" t="str">
         <v/>
       </c>
+      <c r="U88" t="str">
+        <v/>
+      </c>
+      <c r="V88" t="str">
+        <v/>
+      </c>
+      <c r="W88" t="str">
+        <v/>
+      </c>
+      <c r="X88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
       </c>
       <c r="B89" t="str">
-        <v>2025  02:05 מאת DiSHi-12-31</v>
+        <v>2025  02:17 מאת DiSHi-12-31</v>
       </c>
       <c r="C89" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
@@ -4671,16 +5169,28 @@
       <c r="T89" t="str">
         <v/>
       </c>
+      <c r="U89" t="str">
+        <v/>
+      </c>
+      <c r="V89" t="str">
+        <v/>
+      </c>
+      <c r="W89" t="str">
+        <v/>
+      </c>
+      <c r="X89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+        <v>|אלבום חדש| הפרויקט של דודי לוי ואבטיפוס - הפטריקים (2025)</v>
       </c>
       <c r="B90" t="str">
-        <v>2025  02:04 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C90" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-08</v>
@@ -4733,16 +5243,28 @@
       <c r="T90" t="str">
         <v/>
       </c>
+      <c r="U90" t="str">
+        <v/>
+      </c>
+      <c r="V90" t="str">
+        <v/>
+      </c>
+      <c r="W90" t="str">
+        <v/>
+      </c>
+      <c r="X90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
       </c>
       <c r="B91" t="str">
-        <v>2025  02:03 מאת DiSHi-12-31</v>
+        <v>2025  02:16 מאת DiSHi-12-31</v>
       </c>
       <c r="C91" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-08</v>
@@ -4795,16 +5317,28 @@
       <c r="T91" t="str">
         <v/>
       </c>
+      <c r="U91" t="str">
+        <v/>
+      </c>
+      <c r="V91" t="str">
+        <v/>
+      </c>
+      <c r="W91" t="str">
+        <v/>
+      </c>
+      <c r="X91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+        <v>|אלבום חדש| שיר לוי - ילד מוזר (2025)</v>
       </c>
       <c r="B92" t="str">
-        <v>2025  02:02 מאת DiSHi-12-31</v>
+        <v>2025  02:14 מאת DiSHi-12-31</v>
       </c>
       <c r="C92" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-08</v>
@@ -4857,16 +5391,28 @@
       <c r="T92" t="str">
         <v/>
       </c>
+      <c r="U92" t="str">
+        <v/>
+      </c>
+      <c r="V92" t="str">
+        <v/>
+      </c>
+      <c r="W92" t="str">
+        <v/>
+      </c>
+      <c r="X92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
       </c>
       <c r="B93" t="str">
-        <v>2025  02:01 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C93" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-08</v>
@@ -4919,16 +5465,28 @@
       <c r="T93" t="str">
         <v/>
       </c>
+      <c r="U93" t="str">
+        <v/>
+      </c>
+      <c r="V93" t="str">
+        <v/>
+      </c>
+      <c r="W93" t="str">
+        <v/>
+      </c>
+      <c r="X93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+        <v>|אלבום חדש| פיטר רוט - 50 (2025)</v>
       </c>
       <c r="B94" t="str">
-        <v>2025  02:00 מאת DiSHi-12-31</v>
+        <v>2025  02:13 מאת DiSHi-12-31</v>
       </c>
       <c r="C94" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-08</v>
@@ -4981,16 +5539,28 @@
       <c r="T94" t="str">
         <v/>
       </c>
+      <c r="U94" t="str">
+        <v/>
+      </c>
+      <c r="V94" t="str">
+        <v/>
+      </c>
+      <c r="W94" t="str">
+        <v/>
+      </c>
+      <c r="X94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
       </c>
       <c r="B95" t="str">
-        <v>2025  01:57 מאת DiSHi-12-31</v>
+        <v>2025  02:12 מאת DiSHi-12-31</v>
       </c>
       <c r="C95" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-08</v>
@@ -5043,16 +5613,28 @@
       <c r="T95" t="str">
         <v/>
       </c>
+      <c r="U95" t="str">
+        <v/>
+      </c>
+      <c r="V95" t="str">
+        <v/>
+      </c>
+      <c r="W95" t="str">
+        <v/>
+      </c>
+      <c r="X95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+        <v>|אלבום חדש| אגם בוחבוט - עשרים ואחת (2025)</v>
       </c>
       <c r="B96" t="str">
-        <v>2025  01:56 מאת DiSHi-12-31</v>
+        <v>2025  02:11 מאת DiSHi-12-31</v>
       </c>
       <c r="C96" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-08</v>
@@ -5105,16 +5687,28 @@
       <c r="T96" t="str">
         <v/>
       </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
+      <c r="V96" t="str">
+        <v/>
+      </c>
+      <c r="W96" t="str">
+        <v/>
+      </c>
+      <c r="X96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
       </c>
       <c r="B97" t="str">
-        <v>2025  01:55 מאת DiSHi-12-31</v>
+        <v>2025  02:10 מאת DiSHi-12-31</v>
       </c>
       <c r="C97" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-08</v>
@@ -5167,16 +5761,28 @@
       <c r="T97" t="str">
         <v/>
       </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
+      <c r="V97" t="str">
+        <v/>
+      </c>
+      <c r="W97" t="str">
+        <v/>
+      </c>
+      <c r="X97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+        <v>|אלבום חדש| רבקה זוהר - רסיסים של אור (2025)</v>
       </c>
       <c r="B98" t="str">
-        <v>2025  01:54 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C98" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-08</v>
@@ -5229,16 +5835,28 @@
       <c r="T98" t="str">
         <v/>
       </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
+      <c r="V98" t="str">
+        <v/>
+      </c>
+      <c r="W98" t="str">
+        <v/>
+      </c>
+      <c r="X98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
       </c>
       <c r="B99" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:09 מאת DiSHi-12-31</v>
       </c>
       <c r="C99" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-08</v>
@@ -5291,16 +5909,28 @@
       <c r="T99" t="str">
         <v/>
       </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
+      <c r="V99" t="str">
+        <v/>
+      </c>
+      <c r="W99" t="str">
+        <v/>
+      </c>
+      <c r="X99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+        <v>|אלבום חדש| קורין אלאל וחברים! - קורין אלאל הופעות אחרונות (2025)</v>
       </c>
       <c r="B100" t="str">
-        <v>2025  01:53 מאת DiSHi-12-31</v>
+        <v>2025  02:08 מאת DiSHi-12-31</v>
       </c>
       <c r="C100" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-08</v>
@@ -5353,16 +5983,28 @@
       <c r="T100" t="str">
         <v/>
       </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
+      <c r="V100" t="str">
+        <v/>
+      </c>
+      <c r="W100" t="str">
+        <v/>
+      </c>
+      <c r="X100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>הרשם לחברות מלאה</v>
+        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>2025  02:06 מאת DiSHi-12-31</v>
       </c>
       <c r="C101" t="str">
-        <v>https://rotter.name/nor/members-new.html</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-08</v>
@@ -5415,10 +6057,1058 @@
       <c r="T101" t="str">
         <v/>
       </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
+      <c r="V101" t="str">
+        <v/>
+      </c>
+      <c r="W101" t="str">
+        <v/>
+      </c>
+      <c r="X101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>|אלבום חדש| אהוד בנאי ובנו הנדלר - פליטי הדאב (2025)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C102" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
+        <v/>
+      </c>
+      <c r="V102" t="str">
+        <v/>
+      </c>
+      <c r="W102" t="str">
+        <v/>
+      </c>
+      <c r="X102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025  02:05 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C103" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103" t="str">
+        <v/>
+      </c>
+      <c r="V103" t="str">
+        <v/>
+      </c>
+      <c r="W103" t="str">
+        <v/>
+      </c>
+      <c r="X103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>|אלבום חדש| Imagine פסטיגל - שירי התחרות (2025)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025  02:04 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C104" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104" t="str">
+        <v/>
+      </c>
+      <c r="V104" t="str">
+        <v/>
+      </c>
+      <c r="W104" t="str">
+        <v/>
+      </c>
+      <c r="X104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2025  02:03 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C105" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105" t="str">
+        <v/>
+      </c>
+      <c r="V105" t="str">
+        <v/>
+      </c>
+      <c r="W105" t="str">
+        <v/>
+      </c>
+      <c r="X105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>|אלבום חדש| השמחות - חובות אבודים (2025)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2025  02:02 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C106" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106" t="str">
+        <v/>
+      </c>
+      <c r="V106" t="str">
+        <v/>
+      </c>
+      <c r="W106" t="str">
+        <v/>
+      </c>
+      <c r="X106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2025  02:01 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C107" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+      <c r="U107" t="str">
+        <v/>
+      </c>
+      <c r="V107" t="str">
+        <v/>
+      </c>
+      <c r="W107" t="str">
+        <v/>
+      </c>
+      <c r="X107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>|אלבום חדש| שלמה גרוניך - כמו כוכבים (2025)</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2025  02:00 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C108" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <v/>
+      </c>
+      <c r="V108" t="str">
+        <v/>
+      </c>
+      <c r="W108" t="str">
+        <v/>
+      </c>
+      <c r="X108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>|אלבום חדש| דיוויד ברוזה - BrozaJazz (Paris Alhambra) (2025)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2025  01:57 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C109" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+      <c r="U109" t="str">
+        <v/>
+      </c>
+      <c r="V109" t="str">
+        <v/>
+      </c>
+      <c r="W109" t="str">
+        <v/>
+      </c>
+      <c r="X109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>|אלבום חדש| יוני רועה - מפוזרים (2025)</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2025  01:56 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C110" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+      <c r="U110" t="str">
+        <v/>
+      </c>
+      <c r="V110" t="str">
+        <v/>
+      </c>
+      <c r="W110" t="str">
+        <v/>
+      </c>
+      <c r="X110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>|אלבום חדש| אתניקס - איטליה (2025)</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2025  01:55 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C111" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24408&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+      <c r="U111" t="str">
+        <v/>
+      </c>
+      <c r="V111" t="str">
+        <v/>
+      </c>
+      <c r="W111" t="str">
+        <v/>
+      </c>
+      <c r="X111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>|אלבום חדש| התקווה 6 - ויהי אור (2025)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2025  01:54 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C112" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24429&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+      <c r="U112" t="str">
+        <v/>
+      </c>
+      <c r="V112" t="str">
+        <v/>
+      </c>
+      <c r="W112" t="str">
+        <v/>
+      </c>
+      <c r="X112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>|אלבום חדש| שלומי סרנגה - איפרכו (2025)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C113" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24430&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+      <c r="U113" t="str">
+        <v/>
+      </c>
+      <c r="V113" t="str">
+        <v/>
+      </c>
+      <c r="W113" t="str">
+        <v/>
+      </c>
+      <c r="X113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>|אלבום חדש| שאנן סטריט ודי ג׳יי מש - באתי לבדר (2025)</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2025  01:53 מאת DiSHi-12-31</v>
+      </c>
+      <c r="C114" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24431&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+      <c r="U114" t="str">
+        <v/>
+      </c>
+      <c r="V114" t="str">
+        <v/>
+      </c>
+      <c r="W114" t="str">
+        <v/>
+      </c>
+      <c r="X114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>הרשם לחברות מלאה</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v>https://rotter.name/nor/members-new.html</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+      <c r="U115" t="str">
+        <v/>
+      </c>
+      <c r="V115" t="str">
+        <v/>
+      </c>
+      <c r="W115" t="str">
+        <v/>
+      </c>
+      <c r="X115" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X115"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:O29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  08:41-01-14 | מאת</v>
+        <v>2026  15:58-01-15 | מאת</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -466,18 +466,18 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B3" t="str">
         <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -501,18 +501,18 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>תומר יוסף - 360</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B4" t="str">
-        <v>2025  02:18-12-31 | מאת</v>
+        <v>2026  22:40-01-01 | מאת</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -536,18 +536,18 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:16-12-31 | מאת</v>
+        <v>2025  02:17-12-31 | מאת</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>אברהם טל - חי</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:14-12-31 | מאת</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -606,18 +606,18 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>אברהם טל - חי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="B7" t="str">
         <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -641,18 +641,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:11-12-31 | מאת</v>
+        <v>2025  02:12-12-31 | מאת</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -676,18 +676,18 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:09-12-31 | מאת</v>
+        <v>2025  02:10-12-31 | מאת</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -711,18 +711,18 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:08-12-31 | מאת</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -746,18 +746,18 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:05-12-31 | מאת</v>
+        <v>2025  02:06-12-31 | מאת</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -781,18 +781,18 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:04-12-31 | מאת</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -816,18 +816,18 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>סטטיק - קעקועים</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:02-12-31 | מאת</v>
+        <v>2025  02:03-12-31 | מאת</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -851,18 +851,18 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>סטטיק - קעקועים</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>ליאור נרקיס - דיסוננס</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:00-12-31 | מאת</v>
+        <v>2025  02:01-12-31 | מאת</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -886,47 +886,705 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>ליאור נרקיס - דיסוננס</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025  01:57-12-31 | מאת</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026  08:41-01-14 | מאת</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026  08:40-01-14 | מאת</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025  02:18-12-31 | מאת</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025  02:16-12-31 | מאת</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025  02:14-12-31 | מאת</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025  02:13-12-31 | מאת</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>פיטר רוט - 50</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025  02:11-12-31 | מאת</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>אגם בוחבוט - עשרים ואחת</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025  02:09-12-31 | מאת</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>רבקה זוהר - רסיסים של אור</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025  02:08-12-31 | מאת</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025  02:05-12-31 | מאת</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025  02:04-12-31 | מאת</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025  02:02-12-31 | מאת</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025  02:00-12-31 | מאת</v>
+      </c>
+      <c r="C28" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>יוני רועה - מפוזרים</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B29" t="str">
         <v>2025  01:56-12-31 | מאת</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C29" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D15" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
+      <c r="D29" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
         <v>יוני רועה - מפוזרים</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:S30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  15:58-01-15 | מאת</v>
+        <v>2026  11:47-01-17 | מאת</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -466,18 +466,18 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  08:40-01-14 | מאת</v>
+        <v>2026  15:58-01-15 | מאת</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -501,18 +501,30 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  22:40-01-01 | מאת</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -536,18 +548,30 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>תומר יוסף - 360</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עמיר בניון - לא נוגע בקרקע</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B5" t="str">
-        <v>2025  02:17-12-31 | מאת</v>
+        <v>2026  22:40-01-01 | מאת</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -571,18 +595,30 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>עמיר בניון - לא נוגע בקרקע</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אברהם טל - חי</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:16-12-31 | מאת</v>
+        <v>2025  02:17-12-31 | מאת</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -606,18 +642,30 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>אברהם טל - חי</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>אברהם טל - חי</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:13-12-31 | מאת</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -641,18 +689,30 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>אברהם טל - חי</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:12-12-31 | מאת</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -676,18 +736,30 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>מיקי גבריאלוב - שלום</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:10-12-31 | מאת</v>
+        <v>2025  02:12-12-31 | מאת</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -711,18 +783,30 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>שלמה גרוניך - תודה אהבה</v>
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:09-12-31 | מאת</v>
+        <v>2025  02:10-12-31 | מאת</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -746,18 +830,30 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>שלמה גרוניך - תודה אהבה</v>
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>חוה אלברשטיין - חמישה שירים</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:06-12-31 | מאת</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -781,18 +877,30 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>חוה אלברשטיין - חמישה שירים</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:05-12-31 | מאת</v>
+        <v>2025  02:06-12-31 | מאת</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -816,18 +924,30 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>סטטיק - קעקועים</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:03-12-31 | מאת</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -851,18 +971,30 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>סטטיק - קעקועים</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ליאור נרקיס - דיסוננס</v>
+        <v>סטטיק - קעקועים</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:01-12-31 | מאת</v>
+        <v>2025  02:03-12-31 | מאת</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -886,18 +1018,30 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>ליאור נרקיס - דיסוננס</v>
+        <v>סטטיק - קעקועים</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
+        <v>ליאור נרקיס - דיסוננס</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  01:57-12-31 | מאת</v>
+        <v>2025  02:01-12-31 | מאת</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -921,18 +1065,30 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
+        <v>ליאור נרקיס - דיסוננס</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
       </c>
       <c r="B16" t="str">
-        <v>2026  08:41-01-14 | מאת</v>
+        <v>2025  01:57-12-31 | מאת</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -956,7 +1112,7 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -973,13 +1129,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B17" t="str">
-        <v>2026  08:40-01-14 | מאת</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -1003,7 +1159,7 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1015,18 +1171,30 @@
         <v/>
       </c>
       <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>2025  02:18-12-31 | מאת</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1050,7 +1218,7 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1062,18 +1230,30 @@
         <v/>
       </c>
       <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:16-12-31 | מאת</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1097,7 +1277,7 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1109,18 +1289,30 @@
         <v/>
       </c>
       <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:14-12-31 | מאת</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1144,7 +1336,7 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1156,18 +1348,30 @@
         <v/>
       </c>
       <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:13-12-31 | מאת</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1191,7 +1395,7 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1203,18 +1407,30 @@
         <v/>
       </c>
       <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:11-12-31 | מאת</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1238,7 +1454,7 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1250,18 +1466,30 @@
         <v/>
       </c>
       <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:09-12-31 | מאת</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1285,7 +1513,7 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1297,18 +1525,30 @@
         <v/>
       </c>
       <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:08-12-31 | מאת</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1332,7 +1572,7 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1344,18 +1584,30 @@
         <v/>
       </c>
       <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:05-12-31 | מאת</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1379,7 +1631,7 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1391,18 +1643,30 @@
         <v/>
       </c>
       <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:04-12-31 | מאת</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1426,7 +1690,7 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1438,18 +1702,30 @@
         <v/>
       </c>
       <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:02-12-31 | מאת</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1473,7 +1749,7 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1485,18 +1761,30 @@
         <v/>
       </c>
       <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:00-12-31 | מאת</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1520,7 +1808,7 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1532,59 +1820,142 @@
         <v/>
       </c>
       <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025  02:00-12-31 | מאת</v>
+      </c>
+      <c r="C29" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v>יוני רועה - מפוזרים</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B30" t="str">
         <v>2025  01:56-12-31 | מאת</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C30" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D29" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
+      <c r="D30" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
         <v>יוני רועה - מפוזרים</v>
       </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:W31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:47-01-17 | מאת</v>
+        <v>2026  11:48-01-17 | מאת</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-17</v>
@@ -466,21 +466,21 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  15:58-01-15 | מאת</v>
+        <v>2026  11:47-01-17 | מאת</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -501,7 +501,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -518,13 +518,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:40-01-14 | מאת</v>
+        <v>2026  15:58-01-15 | מאת</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>תומר יוסף - 360</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -560,18 +560,30 @@
         <v/>
       </c>
       <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B5" t="str">
-        <v>2026  22:40-01-01 | מאת</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -595,7 +607,7 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -607,18 +619,30 @@
         <v/>
       </c>
       <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמיר בניון - לא נוגע בקרקע</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:17-12-31 | מאת</v>
+        <v>2026  22:40-01-01 | מאת</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -642,7 +666,7 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>עמיר בניון - לא נוגע בקרקע</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -654,18 +678,30 @@
         <v/>
       </c>
       <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אברהם טל - חי</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:16-12-31 | מאת</v>
+        <v>2025  02:17-12-31 | מאת</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -689,7 +725,7 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>אברהם טל - חי</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -701,18 +737,30 @@
         <v/>
       </c>
       <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>אברהם טל - חי</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:13-12-31 | מאת</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -736,7 +784,7 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>אברהם טל - חי</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -748,18 +796,30 @@
         <v/>
       </c>
       <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:12-12-31 | מאת</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -783,7 +843,7 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -795,18 +855,30 @@
         <v/>
       </c>
       <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:10-12-31 | מאת</v>
+        <v>2025  02:12-12-31 | מאת</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -830,7 +902,7 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -842,18 +914,30 @@
         <v/>
       </c>
       <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>שלמה גרוניך - תודה אהבה</v>
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:09-12-31 | מאת</v>
+        <v>2025  02:10-12-31 | מאת</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -877,7 +961,7 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>שלמה גרוניך - תודה אהבה</v>
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -889,18 +973,30 @@
         <v/>
       </c>
       <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>חוה אלברשטיין - חמישה שירים</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:06-12-31 | מאת</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -924,7 +1020,7 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>חוה אלברשטיין - חמישה שירים</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -936,18 +1032,30 @@
         <v/>
       </c>
       <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:05-12-31 | מאת</v>
+        <v>2025  02:06-12-31 | מאת</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -971,7 +1079,7 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -983,18 +1091,30 @@
         <v/>
       </c>
       <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>סטטיק - קעקועים</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:03-12-31 | מאת</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -1018,7 +1138,7 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>סטטיק - קעקועים</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1030,18 +1150,30 @@
         <v/>
       </c>
       <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ליאור נרקיס - דיסוננס</v>
+        <v>סטטיק - קעקועים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:01-12-31 | מאת</v>
+        <v>2025  02:03-12-31 | מאת</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -1065,7 +1197,7 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>ליאור נרקיס - דיסוננס</v>
+        <v>סטטיק - קעקועים</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1077,18 +1209,30 @@
         <v/>
       </c>
       <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
+        <v>ליאור נרקיס - דיסוננס</v>
       </c>
       <c r="B16" t="str">
-        <v>2025  01:57-12-31 | מאת</v>
+        <v>2025  02:01-12-31 | מאת</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -1112,7 +1256,7 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
+        <v>ליאור נרקיס - דיסוננס</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1124,18 +1268,30 @@
         <v/>
       </c>
       <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
       </c>
       <c r="B17" t="str">
-        <v>2026  08:41-01-14 | מאת</v>
+        <v>2025  01:57-12-31 | מאת</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24426&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -1159,7 +1315,7 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>דיוויד ברוזה - BrozaJazz Paris Alhambra</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1188,13 +1344,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B18" t="str">
-        <v>2026  08:40-01-14 | מאת</v>
+        <v>2026  08:41-01-14 | מאת</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1218,7 +1374,7 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1242,18 +1398,30 @@
         <v/>
       </c>
       <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B19" t="str">
-        <v>2025  02:18-12-31 | מאת</v>
+        <v>2026  08:40-01-14 | מאת</v>
       </c>
       <c r="C19" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1277,7 +1445,7 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1301,18 +1469,30 @@
         <v/>
       </c>
       <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B20" t="str">
-        <v>2025  02:16-12-31 | מאת</v>
+        <v>2025  02:18-12-31 | מאת</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1336,7 +1516,7 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1360,18 +1540,30 @@
         <v/>
       </c>
       <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B21" t="str">
-        <v>2025  02:14-12-31 | מאת</v>
+        <v>2025  02:16-12-31 | מאת</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1395,7 +1587,7 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1419,18 +1611,30 @@
         <v/>
       </c>
       <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B22" t="str">
-        <v>2025  02:13-12-31 | מאת</v>
+        <v>2025  02:14-12-31 | מאת</v>
       </c>
       <c r="C22" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1454,7 +1658,7 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1478,18 +1682,30 @@
         <v/>
       </c>
       <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B23" t="str">
-        <v>2025  02:11-12-31 | מאת</v>
+        <v>2025  02:13-12-31 | מאת</v>
       </c>
       <c r="C23" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1513,7 +1729,7 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1537,18 +1753,30 @@
         <v/>
       </c>
       <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B24" t="str">
-        <v>2025  02:09-12-31 | מאת</v>
+        <v>2025  02:11-12-31 | מאת</v>
       </c>
       <c r="C24" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1572,7 +1800,7 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1596,18 +1824,30 @@
         <v/>
       </c>
       <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B25" t="str">
-        <v>2025  02:08-12-31 | מאת</v>
+        <v>2025  02:09-12-31 | מאת</v>
       </c>
       <c r="C25" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1631,7 +1871,7 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1655,18 +1895,30 @@
         <v/>
       </c>
       <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B26" t="str">
-        <v>2025  02:05-12-31 | מאת</v>
+        <v>2025  02:08-12-31 | מאת</v>
       </c>
       <c r="C26" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1690,7 +1942,7 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1714,18 +1966,30 @@
         <v/>
       </c>
       <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B27" t="str">
-        <v>2025  02:04-12-31 | מאת</v>
+        <v>2025  02:05-12-31 | מאת</v>
       </c>
       <c r="C27" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1749,7 +2013,7 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1773,18 +2037,30 @@
         <v/>
       </c>
       <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B28" t="str">
-        <v>2025  02:02-12-31 | מאת</v>
+        <v>2025  02:04-12-31 | מאת</v>
       </c>
       <c r="C28" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1808,7 +2084,7 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1832,18 +2108,30 @@
         <v/>
       </c>
       <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B29" t="str">
-        <v>2025  02:00-12-31 | מאת</v>
+        <v>2025  02:02-12-31 | מאת</v>
       </c>
       <c r="C29" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
@@ -1867,7 +2155,7 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>שלמה גרוניך - כמו כוכבים</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1891,71 +2179,166 @@
         <v/>
       </c>
       <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2025  02:00-12-31 | מאת</v>
+      </c>
+      <c r="C30" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24420&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>שלמה גרוניך - כמו כוכבים</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
         <v>יוני רועה - מפוזרים</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B31" t="str">
         <v>2025  01:56-12-31 | מאת</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C31" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24428&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D30" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
-      <c r="K30" t="str">
+      <c r="D31" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
         <v>יוני רועה - מפוזרים</v>
       </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-      <c r="P30" t="str">
-        <v/>
-      </c>
-      <c r="Q30" t="str">
-        <v/>
-      </c>
-      <c r="R30" t="str">
-        <v/>
-      </c>
-      <c r="S30" t="str">
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לא המשוגע היחידי (2026)</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:17-01-18</v>
+        <v>2026  11:10-01-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24440&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -466,18 +466,18 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לא המשוגע היחידי (2026)</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לייב מופע הינדיקים 2024</v>
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  11:47-01-17</v>
+        <v>2026  11:48-01-17</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -501,18 +501,18 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>|אלבום חדש| חנן בן ארי - לייב מופע הינדיקים 2024</v>
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 (2026)</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>2026  08:41-01-14</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -536,18 +536,18 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>|אלבום חדש| תומר יוסף - 360 (2026)</v>
+        <v>עדן בן זקן - רולקס וקסקט</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026  22:40-01-01</v>
+        <v>2026  08:40-01-14</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:17-12-31</v>
+        <v>2025  02:18-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -606,18 +606,18 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>|אלבום חדש| עמיר בניון - לא נוגע בקרקע (2025)</v>
+        <v>אייל גולן - בית מפואר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
       <c r="B7" t="str">
         <v>2025  02:16-12-31</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -641,18 +641,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>|אלבום חדש| אברהם טל - חי (2025)</v>
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2025  02:14-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -676,18 +676,18 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>|אלבום חדש| מיקי גבריאלוב - שלום (2025)</v>
+        <v>שיר לוי - ילד מוזר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:12-12-31</v>
+        <v>2025  02:13-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -711,18 +711,18 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>|אלבום חדש| בזכרי ימים ימימה - מחווה לצלילי הכרם (2025)</v>
+        <v>פיטר רוט - 50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:10-12-31</v>
+        <v>2025  02:11-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -746,18 +746,18 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>|אלבום חדש| עדן בן זקן - עוד פעם סטלה עוד פעם דכאון (2025)</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B11" t="str">
         <v>2025  02:09-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -781,18 +781,18 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>|אלבום חדש| שלמה גרוניך - תודה אהבה (2025)</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:06-12-31</v>
+        <v>2025  02:08-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -816,18 +816,18 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>|אלבום חדש| חוה אלברשטיין - חמישה שירים (2025)</v>
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
       <c r="B13" t="str">
         <v>2025  02:05-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -851,18 +851,18 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>|אלבום חדש| הפרויקט של עידן רייכל - עד סוף העולם (2025)</v>
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:03-12-31</v>
+        <v>2025  02:04-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -886,18 +886,18 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>|אלבום חדש| סטטיק - קעקועים (2025)</v>
+        <v>Imagine פסטיגל - שירי התחרות</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:01-12-31</v>
+        <v>2025  02:02-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24423&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -921,7 +921,7 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>|אלבום חדש| ליאור נרקיס - דיסוננס (2025)</v>
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>מיקי גבריאלוב - שלום</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23:52</v>
+        <v>22:43</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>מיקי גבריאלוב - שלום</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>02:12</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>02:10</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -474,22 +474,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>נדב גדג’ - בלי יד על הדופק</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-12-31</v>
+        <v>2026-01-22</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>02:12</v>
+        <v>23:52</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,468 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>נדב גדג’ - בלי יד על הדופק</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>11:48</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>08:41</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עדן בן זקן - רולקס וקסקט</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C6" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>08:40</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>02:18</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אייל גולן - בית מפואר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>02:16</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>02:14</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>שיר לוי - ילד מוזר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>02:12</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B11" t="str">
         <v>2025-12-31</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C11" t="str">
         <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
       </c>
-      <c r="D4" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
+      <c r="D11" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>02:10</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>02:08</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>02:05</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>02:04</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>Imagine פסטיגל - שירי התחרות</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>השמחות - חובות אבודים</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-12-31</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>02:02</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>השמחות - חובות אבודים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24401&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:43</v>
+        <v>22:45</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקי גבריאלוב - שלום</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>חנן בן ארי - לא המשוגע היחידי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24440&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23:52</v>
+        <v>15:38</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>חנן בן ארי - לא המשוגע היחידי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-17</v>
+        <v>2026-01-21</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11:48</v>
+        <v>11:10</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,27 +545,27 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-14</v>
+        <v>2026-01-17</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>08:41</v>
+        <v>11:47</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-14</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,27 +621,27 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>תומר יוסף - 360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-12-31</v>
+        <v>2026-01-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>02:18</v>
+        <v>22:40</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -659,27 +659,27 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
       <c r="B8" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>02:16</v>
+        <v>02:17</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -697,27 +697,27 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>אברהם טל - חי</v>
       </c>
       <c r="B9" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>02:14</v>
+        <v>02:16</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -735,27 +735,27 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>אברהם טל - חי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B10" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24406&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>02:12</v>
+        <v>02:13</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -773,27 +773,27 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>בזכרי ימים ימימה - מחווה לצלילי הכרם</v>
+        <v>פיטר רוט - 50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B11" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24405&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>02:10</v>
+        <v>02:11</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -811,27 +811,27 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>עדן בן זקן - עוד פעם סטלה עוד פעם דכאון</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B12" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>02:08</v>
+        <v>02:09</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -849,27 +849,27 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
       <c r="B13" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>02:05</v>
+        <v>02:06</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -887,27 +887,27 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
       <c r="B14" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>02:04</v>
+        <v>02:05</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,27 +925,27 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>סטטיק - קעקועים</v>
       </c>
       <c r="B15" t="str">
         <v>2025-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>02:02</v>
+        <v>02:03</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>סטטיק - קעקועים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>אייל גולן - GOLD 2025</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24444&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24446&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:24</v>
+        <v>00:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>אייל גולן - GOLD 2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
+        <v>דודו טסה - אי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24445&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24449&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
+        <v>דודו טסה - אי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
+        <v>אתי אנקרי - אורייתא</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24443&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24447&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>07:49</v>
+        <v>19:23</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,50 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24448&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>00:30</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
+        <v>אתי אנקרי - אורייתא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - GOLD 2025</v>
+        <v>אייל גולן - בדרך ל-30 EP</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24446&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24450&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>00:20</v>
+        <v>04:00</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - GOLD 2025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>דודו טסה - אי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24449&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>19:23</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>דודו טסה - אי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אתי אנקרי - אורייתא</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24447&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>19:23</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אתי אנקרי - אורייתא</v>
+        <v>אייל גולן - בדרך ל-30 EP</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - בדרך ל-30 EP</v>
+        <v>אילן וירצברג - אילן בן עשרים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24450&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24451&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>04:00</v>
+        <v>22:01</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - בדרך ל-30 EP</v>
+        <v>אילן וירצברג - אילן בן עשרים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אילן וירצברג - אילן בן עשרים</v>
+        <v>עומר אדם - חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24451&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24453&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:01</v>
+        <v>20:42</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אילן וירצברג - אילן בן עשרים</v>
+        <v>עומר אדם - חלק מהנצח</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם - חלק מהנצח</v>
+        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24453&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24454&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:42</v>
+        <v>20:44</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם - חלק מהנצח</v>
+        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24454&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:44</v>
+        <v>13:35</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13:35</v>
+        <v>22:41</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:41</v>
+        <v>15:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אפרת גוש - לרדוף אחרי השמש</v>
+        <v>אייל גולן - 30 חלק ב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24462&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15:20</v>
+        <v>16:05</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אפרת גוש - לרדוף אחרי השמש</v>
+        <v>אייל גולן - 30 חלק ב</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אגם בוחבוט - פריפריה אקספרס</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24460&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>15:58</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אגם בוחבוט - פריפריה אקספרס</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24458&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>15:52</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>עידן רייכל - הד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24462&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24457&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16:05</v>
+        <v>01:19</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>עידן רייכל - הד</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-27</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24460&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24461&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15:58</v>
+        <v>16:00</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24458&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>15:52</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידן רייכל - הד</v>
+        <v>סאבלימינל - ימים טובים באים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-28</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24457&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24459&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-28</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>01:19</v>
+        <v>08:26</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עידן רייכל - הד</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אייל גולן - 30 - חלק א</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24461&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אייל גולן - 30 - חלק א</v>
+        <v>סאבלימינל - ימים טובים באים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23054&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>08:36</v>
+        <v>21:10</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:10</v>
+        <v>21:11</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=21671&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:11</v>
+        <v>11:50</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
+        <v>מיקה קרני ואודי תורג'מן - ברית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=21671&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24466&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-07</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11:50</v>
+        <v>19:31</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
+        <v>מיקה קרני ואודי תורג'מן - ברית</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה קרני ואודי תורג'מן - ברית</v>
+        <v>קובי פרץ - כל עולמי EP</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24466&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24468&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:31</v>
+        <v>19:35</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה קרני ואודי תורג'מן - ברית</v>
+        <v>קובי פרץ - כל עולמי EP</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי פרץ - כל עולמי EP</v>
+        <v>זהו זה - עונה 8</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24468&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:35</v>
+        <v>09:37</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי פרץ - כל עולמי EP</v>
+        <v>זהו זה - עונה 8</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - עונה 8</v>
+        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24191&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>09:37</v>
+        <v>06:50</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - עונה 8</v>
+        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אריק סיני - כל השירים היפים באמת</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24470&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>06:45</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אריק סיני - כל השירים היפים באמת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
+        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24191&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24068&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>06:50</v>
+        <v>06:51</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24470&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>06:45</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
+        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
+        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24068&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24471&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>06:51</v>
+        <v>14:04</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
+        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
+        <v>פרויקט אסי עזר - כל מה שעוזר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24471&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24473&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14:04</v>
+        <v>19:49</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
+        <v>פרויקט אסי עזר - כל מה שעוזר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24473&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24474&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:49</v>
+        <v>09:26</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נינט טייב - אני נינה</v>
+        <v>יובל דיין - יובל דיין לייב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24474&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24475&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>09:26</v>
+        <v>20:02</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נינט טייב - אני נינה</v>
+        <v>יובל דיין - יובל דיין לייב</v>
       </c>
     </row>
   </sheetData>
